--- a/src/constants/i18n/script/i18n.xlsx
+++ b/src/constants/i18n/script/i18n.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="common"/>
@@ -22,7 +22,7 @@
     <t>encode</t>
   </si>
   <si>
-    <t>cn</t>
+    <t>zh-CN</t>
   </si>
   <si>
     <t>en</t>
@@ -7072,7 +7072,7 @@
     <col min="26" max="26" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7106,7 +7106,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A2" s="2" t="s">
         <v>56</v>
       </c>
@@ -7140,7 +7140,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A3" s="2" t="s">
         <v>59</v>
       </c>
@@ -7174,7 +7174,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A4" s="2" t="s">
         <v>62</v>
       </c>

--- a/src/constants/i18n/script/i18n.xlsx
+++ b/src/constants/i18n/script/i18n.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="295">
   <si>
     <t>encode</t>
   </si>
@@ -116,6 +116,15 @@
   </si>
   <si>
     <t>Price</t>
+  </si>
+  <si>
+    <t>totalCurrency</t>
+  </si>
+  <si>
+    <t>总{symbol}</t>
+  </si>
+  <si>
+    <t>Total {symbol}</t>
   </si>
   <si>
     <t>connect</t>
@@ -931,6 +940,9 @@
   <si>
     <t>Home</t>
   </si>
+  <si>
+    <t/>
+  </si>
 </sst>
 </file>
 
@@ -952,15 +964,15 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -991,7 +1003,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1002,10 +1014,13 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1313,32 +1328,32 @@
   <dimension ref="A1:Z194"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="21.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="40.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="54.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="21.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="40.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="4" width="54.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
@@ -1377,13 +1392,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18" customFormat="1" s="1">
       <c r="A2" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -1411,13 +1426,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A3" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -1445,13 +1460,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A4" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>185</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -1479,13 +1494,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A5" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -1513,13 +1528,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A6" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>191</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -1547,13 +1562,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A7" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -1581,13 +1596,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A8" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -1615,13 +1630,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A9" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -1649,13 +1664,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A10" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -1683,13 +1698,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A11" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -1717,13 +1732,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A12" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -1751,13 +1766,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A13" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -1785,13 +1800,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A14" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -1819,13 +1834,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A15" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -1853,13 +1868,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A16" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -1887,13 +1902,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A17" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -1921,13 +1936,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A18" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -1955,13 +1970,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A19" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -1989,13 +2004,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A20" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -2023,13 +2038,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A21" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -2057,13 +2072,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A22" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -2091,13 +2106,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A23" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -2125,13 +2140,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A24" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -2159,13 +2174,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A25" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -2193,13 +2208,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A26" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -2227,13 +2242,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A27" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -2261,13 +2276,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A28" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -2295,13 +2310,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A29" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
@@ -2329,13 +2344,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A30" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -2363,13 +2378,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A31" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -2397,13 +2412,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A32" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -2431,13 +2446,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A33" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
@@ -2465,13 +2480,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A34" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
@@ -2499,13 +2514,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A35" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
@@ -2533,13 +2548,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A36" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -2567,13 +2582,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A37" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -2601,13 +2616,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A38" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -2635,13 +2650,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A39" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -2669,13 +2684,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A40" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
@@ -2703,13 +2718,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A41" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
@@ -2737,13 +2752,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A42" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
@@ -2771,13 +2786,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A43" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
@@ -2804,9 +2819,15 @@
       <c r="Z43" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
+      <c r="A44" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>294</v>
+      </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
@@ -7044,32 +7065,32 @@
   <dimension ref="A1:Z195"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="26.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="40.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="54.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="26.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="40.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="4" width="54.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5" customFormat="1" s="1">
@@ -7108,13 +7129,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -7142,13 +7163,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A3" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -7176,13 +7197,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A4" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -7210,13 +7231,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A5" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -7244,13 +7265,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A6" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -7278,13 +7299,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A7" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -7312,13 +7333,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A8" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -7346,13 +7367,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A9" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -7380,13 +7401,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A10" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -7414,13 +7435,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A11" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -7448,13 +7469,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A12" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -7482,13 +7503,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A13" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -7516,13 +7537,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A14" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -7550,13 +7571,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -7584,13 +7605,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A16" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -7618,13 +7639,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A17" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -7652,13 +7673,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A18" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -7686,13 +7707,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="36" customFormat="1" s="1">
       <c r="A19" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -7720,13 +7741,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A20" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -7754,13 +7775,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A21" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -7788,13 +7809,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A22" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -7822,13 +7843,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A23" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -7856,13 +7877,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A24" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -7890,13 +7911,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A25" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -7924,13 +7945,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A26" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -7958,13 +7979,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A27" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -7992,13 +8013,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A28" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -8026,13 +8047,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A29" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
@@ -8060,13 +8081,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A30" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -8094,13 +8115,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A31" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -8128,13 +8149,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A32" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -8162,13 +8183,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A33" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
@@ -8196,13 +8217,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A34" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
@@ -8230,13 +8251,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A35" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
@@ -8264,13 +8285,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A36" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -8298,13 +8319,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A37" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -8332,13 +8353,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A38" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -8366,13 +8387,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A39" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -8400,13 +8421,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A40" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
@@ -8434,13 +8455,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A41" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
@@ -8468,13 +8489,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A42" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
@@ -8502,13 +8523,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A43" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
@@ -8593,7 +8614,7 @@
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
-      <c r="C46" s="4"/>
+      <c r="C46" s="3"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
@@ -12803,32 +12824,32 @@
   <dimension ref="A1:Z195"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="26.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="40.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="54.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="26.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="40.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="4" width="54.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5" customFormat="1" s="1">
@@ -12867,13 +12888,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -12901,13 +12922,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -12935,13 +12956,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -12969,13 +12990,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -13003,13 +13024,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -13037,13 +13058,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A7" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -13071,13 +13092,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -13105,13 +13126,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A9" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -13196,7 +13217,7 @@
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="4"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -14148,7 +14169,7 @@
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
-      <c r="C46" s="4"/>
+      <c r="C46" s="3"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
@@ -18358,35 +18379,35 @@
   <dimension ref="A1:Z195"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="26.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="40.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="54.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="26.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="40.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="4" width="54.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -18420,7 +18441,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -18454,7 +18475,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -18488,7 +18509,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -18522,7 +18543,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -18556,7 +18577,7 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -18590,7 +18611,7 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
@@ -18624,7 +18645,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
@@ -18658,7 +18679,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -18692,7 +18713,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21" customFormat="1" s="1">
       <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
@@ -18761,9 +18782,15 @@
       <c r="Z11" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -19715,7 +19742,7 @@
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
-      <c r="C46" s="4"/>
+      <c r="C46" s="3"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
